--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -54,14 +54,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结算币别</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否含税</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
@@ -262,6 +254,239 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>地址类型</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>收款条件</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售数量</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售单价</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否赠品</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否补发</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单据日期</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单据类型</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>序号</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>交货方式</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,7 +512,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>地址类型</t>
+      <t>结算币别</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -312,190 +537,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>收款条件</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SKU</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>销售数量</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>销售单价</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否赠品</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否补发</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>单据日期</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>单据类型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>序号</t>
+      <t>是否含税</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -946,28 +988,28 @@
   <sheetData>
     <row r="1" spans="1:36" s="1" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="A1" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -976,10 +1018,10 @@
         <v>2</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>3</v>
@@ -994,13 +1036,13 @@
         <v>6</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>8</v>
@@ -1009,49 +1051,49 @@
         <v>9</v>
       </c>
       <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AB1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AD1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:36">
@@ -1059,6 +1101,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1:Y1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AG$1:$AG$2</definedName>
+  </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
@@ -60,10 +63,6 @@
     <t>税率(%)</t>
   </si>
   <si>
-    <t>是否关闭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>*</t>
     </r>
@@ -538,6 +537,31 @@
         <scheme val="minor"/>
       </rPr>
       <t>是否含税</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否关闭</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -988,28 +1012,28 @@
   <sheetData>
     <row r="1" spans="1:36" s="1" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="A1" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>1</v>
@@ -1018,10 +1042,10 @@
         <v>2</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>3</v>
@@ -1036,13 +1060,13 @@
         <v>6</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>8</v>
@@ -1051,46 +1075,46 @@
         <v>9</v>
       </c>
       <c r="V1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="AF1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AG1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="AI1" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AJ1" s="3" t="s">
         <v>10</v>
@@ -1101,9 +1125,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1:Y1048576">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1:Y1048576 G1:G1048576 AG1:AG1048576 AH1:AH1048576 AI1:AI1048576">
       <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576">
+      <formula1>"B2B订单,售后订单-补/换/赠"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576">
+      <formula1>"EXW,FOB,FCA,DAP,DDU,DDP"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1:W1048576">
+      <formula1>"自提,发货"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z1:Z1048576">
+      <formula1>"货代地址,收货地址,公司地址"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA1:AA1048576">
+      <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <r>
       <rPr>
@@ -552,6 +552,9 @@
       </rPr>
       <t>是否关闭</t>
     </r>
+  </si>
+  <si>
+    <t>EXW</t>
   </si>
 </sst>
 </file>
@@ -1211,8 +1214,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1609,46 +1615,46 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:37">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -1657,72 +1663,83 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AI1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AK1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="3:3">
+    <row r="2" s="2" customFormat="1" spans="3:15">
       <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="O2" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="6">

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AH$1:$AH$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AJ$1:$AJ$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -165,6 +165,28 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单据子类型</t>
+    </r>
+  </si>
+  <si>
     <t>是否收取运费</t>
   </si>
   <si>
@@ -489,6 +511,9 @@
     <t>税率(%)</t>
   </si>
   <si>
+    <t>含税单价</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -552,6 +577,9 @@
       </rPr>
       <t>是否关闭</t>
     </r>
+  </si>
+  <si>
+    <t>客户PO号</t>
   </si>
   <si>
     <t>EXW</t>
@@ -1219,13 +1247,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1585,7 +1613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1593,92 +1621,93 @@
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="7" width="17.625" customWidth="1"/>
-    <col min="8" max="8" width="25.625" customWidth="1"/>
-    <col min="9" max="11" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="21.125" customWidth="1"/>
-    <col min="13" max="14" width="20.625" customWidth="1"/>
-    <col min="15" max="18" width="15.625" customWidth="1"/>
-    <col min="19" max="23" width="20.625" customWidth="1"/>
-    <col min="24" max="24" width="16.625" customWidth="1"/>
-    <col min="25" max="25" width="12.625" customWidth="1"/>
-    <col min="26" max="26" width="19.625" customWidth="1"/>
-    <col min="27" max="27" width="15.625" customWidth="1"/>
-    <col min="28" max="28" width="26.125" customWidth="1"/>
-    <col min="29" max="29" width="15.625" customWidth="1"/>
-    <col min="30" max="31" width="17.25" customWidth="1"/>
-    <col min="32" max="32" width="15.625" customWidth="1"/>
-    <col min="33" max="33" width="15.75" customWidth="1"/>
-    <col min="34" max="35" width="20.625" customWidth="1"/>
-    <col min="36" max="36" width="15.625" customWidth="1"/>
-    <col min="37" max="37" width="22" customWidth="1"/>
+    <col min="7" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="25.625" customWidth="1"/>
+    <col min="10" max="12" width="20.625" customWidth="1"/>
+    <col min="13" max="13" width="21.125" customWidth="1"/>
+    <col min="14" max="15" width="20.625" customWidth="1"/>
+    <col min="16" max="19" width="15.625" customWidth="1"/>
+    <col min="20" max="24" width="20.625" customWidth="1"/>
+    <col min="25" max="25" width="16.625" customWidth="1"/>
+    <col min="26" max="26" width="12.625" customWidth="1"/>
+    <col min="27" max="27" width="19.625" customWidth="1"/>
+    <col min="28" max="28" width="15.625" customWidth="1"/>
+    <col min="29" max="29" width="26.125" customWidth="1"/>
+    <col min="30" max="30" width="15.625" customWidth="1"/>
+    <col min="31" max="32" width="17.25" customWidth="1"/>
+    <col min="33" max="33" width="15.625" customWidth="1"/>
+    <col min="34" max="34" width="15.75" customWidth="1"/>
+    <col min="35" max="35" width="15.875" customWidth="1"/>
+    <col min="36" max="37" width="20.625" customWidth="1"/>
+    <col min="38" max="39" width="15.625" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:37">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:40">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="6" t="s">
@@ -1687,22 +1716,22 @@
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="7" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="5" t="s">
@@ -1714,53 +1743,63 @@
       <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AI1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="5" t="s">
-        <v>27</v>
+      <c r="AK1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="3:15">
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="O2" s="2" t="s">
-        <v>36</v>
+    <row r="2" s="1" customFormat="1" spans="7:16">
+      <c r="G2"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"B2B订单,售后订单-补/换/赠"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576 Y$1:Y$1048576 AH$1:AJ$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+      <formula1>"线下订单,线上订单,赠品订单,赠品补发,红人样品,部门领用,评价返现,补偿赠券,福袋抽奖,换货补发,补发,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AJ$1:AL$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O$1:O$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
       <formula1>"EXW,FOB,FCA,DAP,DDU,DDP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
       <formula1>"自提,发货"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:Z$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA$1:AA$1048576">
       <formula1>"货代地址,收货地址,公司地址"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA$1:AA$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB$1:AB$1048576">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <r>
       <rPr>
@@ -580,6 +580,9 @@
   </si>
   <si>
     <t>客户PO号</t>
+  </si>
+  <si>
+    <t>目的地</t>
   </si>
   <si>
     <t>EXW</t>
@@ -1613,7 +1616,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1640,10 +1643,10 @@
     <col min="35" max="35" width="15.875" customWidth="1"/>
     <col min="36" max="37" width="20.625" customWidth="1"/>
     <col min="38" max="39" width="15.625" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="40" max="41" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:40">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1762,6 +1765,9 @@
         <v>38</v>
       </c>
       <c r="AN1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1773,7 +1779,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -580,9 +580,6 @@
   </si>
   <si>
     <t>客户PO号</t>
-  </si>
-  <si>
-    <t>目的地</t>
   </si>
   <si>
     <t>EXW</t>
@@ -1616,7 +1613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1643,10 +1640,10 @@
     <col min="35" max="35" width="15.875" customWidth="1"/>
     <col min="36" max="37" width="20.625" customWidth="1"/>
     <col min="38" max="39" width="15.625" customWidth="1"/>
-    <col min="40" max="41" width="22" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:40">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1765,9 +1762,6 @@
         <v>38</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1779,7 +1773,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AJ$1:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AL$1:$AL$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <r>
       <rPr>
@@ -453,6 +453,12 @@
       </rPr>
       <t>收款条件</t>
     </r>
+  </si>
+  <si>
+    <t>订单金额</t>
+  </si>
+  <si>
+    <t>付款流水号</t>
   </si>
   <si>
     <t>备注</t>
@@ -1616,7 +1622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1635,18 +1641,18 @@
     <col min="26" max="26" width="12.625" customWidth="1"/>
     <col min="27" max="27" width="19.625" customWidth="1"/>
     <col min="28" max="28" width="15.625" customWidth="1"/>
-    <col min="29" max="29" width="26.125" customWidth="1"/>
-    <col min="30" max="30" width="15.625" customWidth="1"/>
-    <col min="31" max="32" width="17.25" customWidth="1"/>
-    <col min="33" max="33" width="15.625" customWidth="1"/>
-    <col min="34" max="34" width="15.75" customWidth="1"/>
-    <col min="35" max="35" width="15.875" customWidth="1"/>
-    <col min="36" max="37" width="20.625" customWidth="1"/>
-    <col min="38" max="39" width="15.625" customWidth="1"/>
-    <col min="40" max="41" width="22" customWidth="1"/>
+    <col min="29" max="31" width="26.125" customWidth="1"/>
+    <col min="32" max="32" width="15.625" customWidth="1"/>
+    <col min="33" max="34" width="17.25" customWidth="1"/>
+    <col min="35" max="35" width="15.625" customWidth="1"/>
+    <col min="36" max="36" width="15.75" customWidth="1"/>
+    <col min="37" max="37" width="15.875" customWidth="1"/>
+    <col min="38" max="39" width="20.625" customWidth="1"/>
+    <col min="40" max="41" width="15.625" customWidth="1"/>
+    <col min="42" max="43" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:43">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1734,13 +1740,13 @@
       <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="5" t="s">
@@ -1749,26 +1755,32 @@
       <c r="AH1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AM1" s="6" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="5" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="7:16">
@@ -1779,7 +1791,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +1802,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"线下订单,线上订单,赠品订单,赠品补发,红人样品,部门领用,评价返现,补偿赠券,福袋抽奖,换货补发,补发,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AJ$1:AL$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AL$1:AN$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
@@ -1805,7 +1817,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB$1:AB$1048576">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AJ$1:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$AL$1:$AL$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <r>
       <rPr>
@@ -240,13 +240,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -260,10 +253,34 @@
     </r>
   </si>
   <si>
-    <t>收款日期</t>
-  </si>
-  <si>
-    <t>收款金额</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>收款日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>收款金额</t>
+    </r>
   </si>
   <si>
     <t>贸易条款</t>
@@ -368,13 +385,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -453,6 +463,24 @@
       </rPr>
       <t>收款条件</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>订单金额</t>
+    </r>
+  </si>
+  <si>
+    <t>付款流水号</t>
   </si>
   <si>
     <t>备注</t>
@@ -1245,7 +1273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1263,6 +1291,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1616,7 +1647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1635,18 +1666,18 @@
     <col min="26" max="26" width="12.625" customWidth="1"/>
     <col min="27" max="27" width="19.625" customWidth="1"/>
     <col min="28" max="28" width="15.625" customWidth="1"/>
-    <col min="29" max="29" width="26.125" customWidth="1"/>
-    <col min="30" max="30" width="15.625" customWidth="1"/>
-    <col min="31" max="32" width="17.25" customWidth="1"/>
-    <col min="33" max="33" width="15.625" customWidth="1"/>
-    <col min="34" max="34" width="15.75" customWidth="1"/>
-    <col min="35" max="35" width="15.875" customWidth="1"/>
-    <col min="36" max="37" width="20.625" customWidth="1"/>
-    <col min="38" max="39" width="15.625" customWidth="1"/>
-    <col min="40" max="41" width="22" customWidth="1"/>
+    <col min="29" max="31" width="26.125" customWidth="1"/>
+    <col min="32" max="32" width="15.625" customWidth="1"/>
+    <col min="33" max="34" width="17.25" customWidth="1"/>
+    <col min="35" max="35" width="15.625" customWidth="1"/>
+    <col min="36" max="36" width="15.75" customWidth="1"/>
+    <col min="37" max="37" width="15.875" customWidth="1"/>
+    <col min="38" max="39" width="20.625" customWidth="1"/>
+    <col min="40" max="41" width="15.625" customWidth="1"/>
+    <col min="42" max="43" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:43">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1686,10 +1717,10 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1719,7 +1750,7 @@
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="5" t="s">
@@ -1731,16 +1762,16 @@
       <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="8" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="5" t="s">
@@ -1749,26 +1780,32 @@
       <c r="AH1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AM1" s="6" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="5" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="7:16">
@@ -1779,7 +1816,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +1827,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"线下订单,线上订单,赠品订单,赠品补发,红人样品,部门领用,评价返现,补偿赠券,福袋抽奖,换货补发,补发,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AJ$1:AL$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AL$1:AN$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
@@ -1805,7 +1842,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB$1:AB$1048576">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -240,13 +240,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -260,10 +253,34 @@
     </r>
   </si>
   <si>
-    <t>收款日期</t>
-  </si>
-  <si>
-    <t>收款金额</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>收款日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>收款金额</t>
+    </r>
   </si>
   <si>
     <t>贸易条款</t>
@@ -368,13 +385,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -455,7 +465,19 @@
     </r>
   </si>
   <si>
-    <t>订单金额</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>订单金额</t>
+    </r>
   </si>
   <si>
     <t>付款流水号</t>
@@ -1251,7 +1273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1269,6 +1291,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1692,10 +1717,10 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1725,7 +1750,7 @@
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="5" t="s">
@@ -1737,7 +1762,7 @@
       <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="5" t="s">
@@ -1746,7 +1771,7 @@
       <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AF1" s="8" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="5" t="s">
@@ -1761,7 +1786,7 @@
       <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AK1" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="3" t="s">

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -554,28 +554,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>是否补发</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否关闭</t>
     </r>
   </si>
   <si>
@@ -1616,7 +1594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1642,11 +1620,11 @@
     <col min="34" max="34" width="15.75" customWidth="1"/>
     <col min="35" max="35" width="15.875" customWidth="1"/>
     <col min="36" max="37" width="20.625" customWidth="1"/>
-    <col min="38" max="39" width="15.625" customWidth="1"/>
-    <col min="40" max="41" width="22" customWidth="1"/>
+    <col min="38" max="38" width="15.625" customWidth="1"/>
+    <col min="39" max="40" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:41">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:40">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1765,21 +1743,13 @@
         <v>38</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="7:16">
       <c r="G2"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +1760,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"线下订单,线上订单,赠品订单,赠品补发,红人样品,部门领用,评价返现,补偿赠券,福袋抽奖,换货补发,补发,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AJ$1:AL$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AJ$1:AK$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
@@ -1805,7 +1775,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB$1:AB$1048576">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AL$1:AL$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <r>
       <rPr>
@@ -240,6 +240,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -254,6 +261,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -269,6 +283,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -385,6 +406,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -466,6 +494,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -582,28 +617,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>是否补发</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否关闭</t>
     </r>
   </si>
   <si>
@@ -1647,7 +1660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="2" max="2" width="15.125" customWidth="1"/>
@@ -1673,11 +1686,11 @@
     <col min="36" max="36" width="15.75" customWidth="1"/>
     <col min="37" max="37" width="15.875" customWidth="1"/>
     <col min="38" max="39" width="20.625" customWidth="1"/>
-    <col min="40" max="41" width="15.625" customWidth="1"/>
-    <col min="42" max="43" width="22" customWidth="1"/>
+    <col min="40" max="40" width="15.625" customWidth="1"/>
+    <col min="41" max="42" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:43">
+    <row r="1" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:42">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1802,21 +1815,13 @@
         <v>40</v>
       </c>
       <c r="AP1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="7:16">
       <c r="G2"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
       <c r="P2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1827,7 +1832,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
       <formula1>"线下订单,线上订单,赠品订单,赠品补发,红人样品,部门领用,评价返现,补偿赠券,福袋抽奖,换货补发,补发,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AL$1:AN$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H$1:H$1048576 Z$1:Z$1048576 AL$1:AM$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
@@ -1842,7 +1847,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB$1:AB$1048576">
       <formula1>"网店销售收款,预收100%,货到收款,多到期日(按金额),月结30天,分期付款,30天后收款"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AN$1:AN$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2bsoExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1818,14 +1818,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="7:16">
+    <row r="2" s="1" customFormat="1" spans="1:42">
       <c r="G2"/>
       <c r="P2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X1 X3:X1048576">
+      <formula1>"自提,发货"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2">
+      <formula1>"渠道订单,卡车订单,自提订单,卡车自提"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"B2B订单,售后订单-补/换/赠"</formula1>
     </dataValidation>
@@ -1837,9 +1843,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
       <formula1>"EXW,FOB,FCA,DAP,DDU,DDP"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
-      <formula1>"自提,发货"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA$1:AA$1048576">
       <formula1>"货代地址,收货地址,公司地址"</formula1>
